--- a/FREVS/pierre towers.xlsx
+++ b/FREVS/pierre towers.xlsx
@@ -686,9 +686,9 @@
           <t>NOI used (revenue minus operating expenses)</t>
         </is>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" t="n" s="9">
         <f>B10-B11</f>
-        <v/>
+        <v>3528000</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
@@ -727,9 +727,9 @@
           <t>Nine-month NOI, annualized × 12/9</t>
         </is>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" t="n" s="6">
         <f>(B14-B15)*12/9</f>
-        <v/>
+        <v>3665333.3333333335</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
@@ -756,11 +756,11 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>0.055</v>
+        <v>0.06</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Same labeled LOW cap rate as the brooks.xlsx.</t>
+          <t>LOW cap rate is 6.0%, widened from the brooks.xlsx 5.5% row.</t>
         </is>
       </c>
     </row>
@@ -974,20 +974,20 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>LOW, fiscal 2025 NOI / 5.5%</t>
-        </is>
-      </c>
-      <c r="B39" s="11">
+          <t>LOW, fiscal 2025 NOI / 6.0%</t>
+        </is>
+      </c>
+      <c r="B39" t="n" s="11">
         <f>B19</f>
-        <v/>
-      </c>
-      <c r="C39" s="9">
+        <v>0.06</v>
+      </c>
+      <c r="C39" t="n" s="9">
         <f>$B$12/B39</f>
-        <v/>
-      </c>
-      <c r="D39" s="13">
+        <v>58800000</v>
+      </c>
+      <c r="D39" t="n" s="13">
         <f>C39/$B$25-1</f>
-        <v/>
+        <v>-0.1720991791</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
@@ -1005,9 +1005,9 @@
         <f>B20</f>
         <v/>
       </c>
-      <c r="C40" s="9">
+      <c r="C40" t="n" s="9">
         <f>$B$12/B40</f>
-        <v/>
+        <v>70560000</v>
       </c>
       <c r="D40" s="13">
         <f>C40/$B$25-1</f>
@@ -1070,16 +1070,16 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Reference, annualized nine-month NOI / 5.5%</t>
-        </is>
-      </c>
-      <c r="B43" s="11">
+          <t>Reference, annualized nine-month NOI / 6.0%</t>
+        </is>
+      </c>
+      <c r="B43" t="n" s="11">
         <f>B19</f>
-        <v/>
-      </c>
-      <c r="C43" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="C43" t="n" s="6">
         <f>$B$16/B43</f>
-        <v/>
+        <v>61088888.8888888955</v>
       </c>
       <c r="D43" s="13">
         <f>C43/$B$25-1</f>
@@ -1111,9 +1111,9 @@
           <t>Ownership</t>
         </is>
       </c>
-      <c r="B101" s="17">
+      <c r="B101" t="n" s="17">
         <f>B5</f>
-        <v/>
+        <v>0.65</v>
       </c>
     </row>
     <row r="102">
@@ -1122,9 +1122,9 @@
           <t>Book carrying value</t>
         </is>
       </c>
-      <c r="B102" s="18">
+      <c r="B102" t="n" s="18">
         <f>B25</f>
-        <v/>
+        <v>71023000</v>
       </c>
     </row>
     <row r="103">
@@ -1133,9 +1133,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="B103" s="18">
+      <c r="B103" t="n" s="18">
         <f>C39</f>
-        <v/>
+        <v>58800000</v>
       </c>
     </row>
     <row r="104">
@@ -1144,9 +1144,9 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="B104" s="18">
+      <c r="B104" t="n" s="18">
         <f>C40</f>
-        <v/>
+        <v>70560000</v>
       </c>
     </row>
     <row r="105">
@@ -1165,9 +1165,9 @@
           <t>Mortgage</t>
         </is>
       </c>
-      <c r="B106" s="18">
+      <c r="B106" t="n" s="18">
         <f>B26</f>
-        <v/>
+        <v>45258000</v>
       </c>
     </row>
     <row r="107">
@@ -1176,9 +1176,9 @@
           <t>NOI used</t>
         </is>
       </c>
-      <c r="B107" s="18">
+      <c r="B107" t="n" s="18">
         <f>B12</f>
-        <v/>
+        <v>3528000</v>
       </c>
     </row>
     <row r="108">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B108" s="20" t="inlineStr">
         <is>
-          <t>Filing NOI (fiscal 2025) capitalized at the brooks.xlsx 5.5% / 5.0% pair. Cap rates are the method; NOI is filed.</t>
+          <t>Filing NOI (fiscal 2025) capitalized at a 6.0% LOW cap rate and the brooks.xlsx 5.0% HIGH cap rate. Cap rates are the method; NOI is filed.</t>
         </is>
       </c>
     </row>
